--- a/rules/SmartDEV_Validation_Rules_Review_Draft.xlsx
+++ b/rules/SmartDEV_Validation_Rules_Review_Draft.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Information\BenefitsIQ\Data Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="473" documentId="13_ncr:1_{2F121D38-B440-4CE0-A36B-6A796900387E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6301AF83-D755-4701-8476-2DDA821C9FFA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{69C4063A-DAA3-4BEF-8B79-FF545140E320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="380" windowWidth="19200" windowHeight="10390" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="380" windowWidth="19200" windowHeight="10390" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -11084,13 +11084,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PersonValidationRules" displayName="PersonValidationRules" ref="A1:V194" totalsRowShown="0">
-  <autoFilter ref="A1:V194" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="BUSINESS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V194" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V187">
     <sortCondition ref="C1:C187"/>
   </sortState>
@@ -11887,7 +11881,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="2" spans="1:23" ht="62.1" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>55</v>
       </c>
@@ -11952,7 +11946,7 @@
       <c r="V2" s="8"/>
       <c r="W2" s="2"/>
     </row>
-    <row r="3" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="3" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A3" s="11" t="s">
         <v>55</v>
       </c>
@@ -12017,7 +12011,7 @@
       <c r="V3" s="8"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="4" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="11" t="s">
         <v>55</v>
       </c>
@@ -12082,7 +12076,7 @@
       <c r="V4" s="8"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="5" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A5" s="11" t="s">
         <v>55</v>
       </c>
@@ -12147,7 +12141,7 @@
       <c r="V5" s="8"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="6" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="11" t="s">
         <v>55</v>
       </c>
@@ -12212,7 +12206,7 @@
       <c r="V6" s="8"/>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="7" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>55</v>
       </c>
@@ -12277,7 +12271,7 @@
       <c r="V7" s="8"/>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="8" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="11" t="s">
         <v>55</v>
       </c>
@@ -12342,7 +12336,7 @@
       <c r="V8" s="8"/>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="9" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A9" s="11" t="s">
         <v>55</v>
       </c>
@@ -12407,7 +12401,7 @@
       <c r="V9" s="8"/>
       <c r="W9" s="2"/>
     </row>
-    <row r="10" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="10" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="11" t="s">
         <v>55</v>
       </c>
@@ -12472,7 +12466,7 @@
       <c r="V10" s="8"/>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="11" spans="1:23" ht="48" customHeight="1">
       <c r="A11" s="11" t="s">
         <v>55</v>
       </c>
@@ -12537,7 +12531,7 @@
       <c r="V11" s="8"/>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="12" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A12" s="11" t="s">
         <v>55</v>
       </c>
@@ -12602,7 +12596,7 @@
       <c r="V12" s="8"/>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="13" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A13" s="11" t="s">
         <v>55</v>
       </c>
@@ -12667,7 +12661,7 @@
       <c r="V13" s="8"/>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="14" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A14" s="11" t="s">
         <v>55</v>
       </c>
@@ -12732,7 +12726,7 @@
       <c r="V14" s="8"/>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="15" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A15" s="11" t="s">
         <v>55</v>
       </c>
@@ -12797,7 +12791,7 @@
       <c r="V15" s="8"/>
       <c r="W15" s="2"/>
     </row>
-    <row r="16" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="16" spans="1:23" ht="48" customHeight="1">
       <c r="A16" s="11" t="s">
         <v>55</v>
       </c>
@@ -12862,7 +12856,7 @@
       <c r="V16" s="8"/>
       <c r="W16" s="2"/>
     </row>
-    <row r="17" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="17" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A17" s="11" t="s">
         <v>55</v>
       </c>
@@ -12927,7 +12921,7 @@
       <c r="V17" s="8"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="18" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A18" s="11" t="s">
         <v>55</v>
       </c>
@@ -12992,7 +12986,7 @@
       <c r="V18" s="8"/>
       <c r="W18" s="2"/>
     </row>
-    <row r="19" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="19" spans="1:23" ht="75.95" customHeight="1">
       <c r="A19" s="11" t="s">
         <v>55</v>
       </c>
@@ -13057,7 +13051,7 @@
       <c r="V19" s="8"/>
       <c r="W19" s="2"/>
     </row>
-    <row r="20" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="20" spans="1:23" ht="75.95" customHeight="1">
       <c r="A20" s="11" t="s">
         <v>55</v>
       </c>
@@ -13122,7 +13116,7 @@
       <c r="V20" s="8"/>
       <c r="W20" s="2"/>
     </row>
-    <row r="21" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="21" spans="1:23" ht="90" customHeight="1">
       <c r="A21" s="11" t="s">
         <v>55</v>
       </c>
@@ -13187,7 +13181,7 @@
       <c r="V21" s="8"/>
       <c r="W21" s="2"/>
     </row>
-    <row r="22" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="22" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A22" s="11" t="s">
         <v>55</v>
       </c>
@@ -13252,7 +13246,7 @@
       <c r="V22" s="8"/>
       <c r="W22" s="2"/>
     </row>
-    <row r="23" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="23" spans="1:23" ht="48" customHeight="1">
       <c r="A23" s="11" t="s">
         <v>55</v>
       </c>
@@ -13317,7 +13311,7 @@
       <c r="V23" s="8"/>
       <c r="W23" s="2"/>
     </row>
-    <row r="24" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="24" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A24" s="11" t="s">
         <v>55</v>
       </c>
@@ -13382,7 +13376,7 @@
       <c r="V24" s="8"/>
       <c r="W24" s="2"/>
     </row>
-    <row r="25" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="25" spans="1:23" ht="90" customHeight="1">
       <c r="A25" s="11" t="s">
         <v>55</v>
       </c>
@@ -13447,7 +13441,7 @@
       <c r="V25" s="8"/>
       <c r="W25" s="2"/>
     </row>
-    <row r="26" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="26" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A26" s="11" t="s">
         <v>55</v>
       </c>
@@ -13512,7 +13506,7 @@
       <c r="V26" s="8"/>
       <c r="W26" s="2"/>
     </row>
-    <row r="27" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="27" spans="1:23" ht="48" customHeight="1">
       <c r="A27" s="11" t="s">
         <v>55</v>
       </c>
@@ -13577,7 +13571,7 @@
       <c r="V27" s="8"/>
       <c r="W27" s="2"/>
     </row>
-    <row r="28" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="28" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A28" s="11" t="s">
         <v>55</v>
       </c>
@@ -13642,7 +13636,7 @@
       <c r="V28" s="8"/>
       <c r="W28" s="2"/>
     </row>
-    <row r="29" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="29" spans="1:23" ht="62.1" customHeight="1">
       <c r="A29" s="11" t="s">
         <v>55</v>
       </c>
@@ -13707,7 +13701,7 @@
       <c r="V29" s="8"/>
       <c r="W29" s="2"/>
     </row>
-    <row r="30" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="30" spans="1:23" ht="62.1" customHeight="1">
       <c r="A30" s="11" t="s">
         <v>55</v>
       </c>
@@ -13772,7 +13766,7 @@
       <c r="V30" s="8"/>
       <c r="W30" s="2"/>
     </row>
-    <row r="31" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="31" spans="1:23" ht="48" customHeight="1">
       <c r="A31" s="11" t="s">
         <v>55</v>
       </c>
@@ -13837,7 +13831,7 @@
       <c r="V31" s="8"/>
       <c r="W31" s="2"/>
     </row>
-    <row r="32" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="32" spans="1:23" ht="48" customHeight="1">
       <c r="A32" s="11" t="s">
         <v>55</v>
       </c>
@@ -13902,7 +13896,7 @@
       <c r="V32" s="8"/>
       <c r="W32" s="2"/>
     </row>
-    <row r="33" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="33" spans="1:23" ht="90" customHeight="1">
       <c r="A33" s="11" t="s">
         <v>55</v>
       </c>
@@ -13967,7 +13961,7 @@
       <c r="V33" s="8"/>
       <c r="W33" s="2"/>
     </row>
-    <row r="34" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="34" spans="1:23" ht="90" customHeight="1">
       <c r="A34" s="11" t="s">
         <v>55</v>
       </c>
@@ -14032,7 +14026,7 @@
       <c r="V34" s="8"/>
       <c r="W34" s="2"/>
     </row>
-    <row r="35" spans="1:23" ht="230.1" hidden="1" customHeight="1">
+    <row r="35" spans="1:23" ht="230.1" customHeight="1">
       <c r="A35" s="11" t="s">
         <v>55</v>
       </c>
@@ -14097,7 +14091,7 @@
       <c r="V35" s="8"/>
       <c r="W35" s="2"/>
     </row>
-    <row r="36" spans="1:23" ht="230.1" hidden="1" customHeight="1">
+    <row r="36" spans="1:23" ht="230.1" customHeight="1">
       <c r="A36" s="11" t="s">
         <v>55</v>
       </c>
@@ -14162,7 +14156,7 @@
       <c r="V36" s="8"/>
       <c r="W36" s="2"/>
     </row>
-    <row r="37" spans="1:23" ht="216" hidden="1" customHeight="1">
+    <row r="37" spans="1:23" ht="216" customHeight="1">
       <c r="A37" s="11" t="s">
         <v>55</v>
       </c>
@@ -14227,7 +14221,7 @@
       <c r="V37" s="8"/>
       <c r="W37" s="2"/>
     </row>
-    <row r="38" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="38" spans="1:23" ht="48" customHeight="1">
       <c r="A38" s="11" t="s">
         <v>55</v>
       </c>
@@ -14292,7 +14286,7 @@
       <c r="V38" s="8"/>
       <c r="W38" s="2"/>
     </row>
-    <row r="39" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="39" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A39" s="11" t="s">
         <v>55</v>
       </c>
@@ -14357,7 +14351,7 @@
       <c r="V39" s="8"/>
       <c r="W39" s="2"/>
     </row>
-    <row r="40" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="40" spans="1:23" ht="48" customHeight="1">
       <c r="A40" s="11" t="s">
         <v>55</v>
       </c>
@@ -14422,7 +14416,7 @@
       <c r="V40" s="8"/>
       <c r="W40" s="2"/>
     </row>
-    <row r="41" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="41" spans="1:23" ht="48" customHeight="1">
       <c r="A41" s="11" t="s">
         <v>55</v>
       </c>
@@ -14487,7 +14481,7 @@
       <c r="V41" s="8"/>
       <c r="W41" s="2"/>
     </row>
-    <row r="42" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="42" spans="1:23" ht="48" customHeight="1">
       <c r="A42" s="11" t="s">
         <v>55</v>
       </c>
@@ -14552,7 +14546,7 @@
       <c r="V42" s="8"/>
       <c r="W42" s="2"/>
     </row>
-    <row r="43" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="43" spans="1:23" ht="90" customHeight="1">
       <c r="A43" s="11" t="s">
         <v>55</v>
       </c>
@@ -14617,7 +14611,7 @@
       <c r="V43" s="8"/>
       <c r="W43" s="2"/>
     </row>
-    <row r="44" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="44" spans="1:23" ht="75.95" customHeight="1">
       <c r="A44" s="11" t="s">
         <v>55</v>
       </c>
@@ -14682,7 +14676,7 @@
       <c r="V44" s="8"/>
       <c r="W44" s="2"/>
     </row>
-    <row r="45" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="45" spans="1:23" ht="75.95" customHeight="1">
       <c r="A45" s="11" t="s">
         <v>55</v>
       </c>
@@ -14747,7 +14741,7 @@
       <c r="V45" s="8"/>
       <c r="W45" s="2"/>
     </row>
-    <row r="46" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="46" spans="1:23" ht="48" customHeight="1">
       <c r="A46" s="11" t="s">
         <v>55</v>
       </c>
@@ -14812,7 +14806,7 @@
       <c r="V46" s="8"/>
       <c r="W46" s="2"/>
     </row>
-    <row r="47" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="47" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A47" s="11" t="s">
         <v>55</v>
       </c>
@@ -14877,7 +14871,7 @@
       <c r="V47" s="8"/>
       <c r="W47" s="2"/>
     </row>
-    <row r="48" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="48" spans="1:23" ht="48" customHeight="1">
       <c r="A48" s="11" t="s">
         <v>55</v>
       </c>
@@ -14942,7 +14936,7 @@
       <c r="V48" s="8"/>
       <c r="W48" s="2"/>
     </row>
-    <row r="49" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="49" spans="1:23" ht="62.1" customHeight="1">
       <c r="A49" s="11" t="s">
         <v>55</v>
       </c>
@@ -15007,7 +15001,7 @@
       <c r="V49" s="8"/>
       <c r="W49" s="2"/>
     </row>
-    <row r="50" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="50" spans="1:23" ht="48" customHeight="1">
       <c r="A50" s="11" t="s">
         <v>55</v>
       </c>
@@ -15072,7 +15066,7 @@
       <c r="V50" s="8"/>
       <c r="W50" s="2"/>
     </row>
-    <row r="51" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="51" spans="1:23" ht="62.1" customHeight="1">
       <c r="A51" s="11" t="s">
         <v>55</v>
       </c>
@@ -15137,7 +15131,7 @@
       <c r="V51" s="8"/>
       <c r="W51" s="2"/>
     </row>
-    <row r="52" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="52" spans="1:23" ht="62.1" customHeight="1">
       <c r="A52" s="11" t="s">
         <v>55</v>
       </c>
@@ -15202,7 +15196,7 @@
       <c r="V52" s="8"/>
       <c r="W52" s="2"/>
     </row>
-    <row r="53" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="53" spans="1:23" ht="62.1" customHeight="1">
       <c r="A53" s="11" t="s">
         <v>55</v>
       </c>
@@ -15267,7 +15261,7 @@
       <c r="V53" s="8"/>
       <c r="W53" s="2"/>
     </row>
-    <row r="54" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="54" spans="1:23" ht="48" customHeight="1">
       <c r="A54" s="11" t="s">
         <v>55</v>
       </c>
@@ -15332,7 +15326,7 @@
       <c r="V54" s="8"/>
       <c r="W54" s="2"/>
     </row>
-    <row r="55" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="55" spans="1:23" ht="48" customHeight="1">
       <c r="A55" s="11" t="s">
         <v>55</v>
       </c>
@@ -15397,7 +15391,7 @@
       <c r="V55" s="8"/>
       <c r="W55" s="2"/>
     </row>
-    <row r="56" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="56" spans="1:23" ht="48" customHeight="1">
       <c r="A56" s="11" t="s">
         <v>55</v>
       </c>
@@ -15462,7 +15456,7 @@
       <c r="V56" s="8"/>
       <c r="W56" s="2"/>
     </row>
-    <row r="57" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="57" spans="1:23" ht="48" customHeight="1">
       <c r="A57" s="11" t="s">
         <v>55</v>
       </c>
@@ -15527,7 +15521,7 @@
       <c r="V57" s="8"/>
       <c r="W57" s="2"/>
     </row>
-    <row r="58" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="58" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A58" s="11" t="s">
         <v>55</v>
       </c>
@@ -15592,7 +15586,7 @@
       <c r="V58" s="8"/>
       <c r="W58" s="2"/>
     </row>
-    <row r="59" spans="1:23" ht="104.1" hidden="1" customHeight="1">
+    <row r="59" spans="1:23" ht="104.1" customHeight="1">
       <c r="A59" s="11" t="s">
         <v>55</v>
       </c>
@@ -15657,7 +15651,7 @@
       <c r="V59" s="8"/>
       <c r="W59" s="2"/>
     </row>
-    <row r="60" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="60" spans="1:23" ht="48" customHeight="1">
       <c r="A60" s="11" t="s">
         <v>55</v>
       </c>
@@ -15722,7 +15716,7 @@
       <c r="V60" s="8"/>
       <c r="W60" s="2"/>
     </row>
-    <row r="61" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="61" spans="1:23" ht="48" customHeight="1">
       <c r="A61" s="11" t="s">
         <v>55</v>
       </c>
@@ -15787,7 +15781,7 @@
       <c r="V61" s="8"/>
       <c r="W61" s="2"/>
     </row>
-    <row r="62" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="62" spans="1:23" ht="48" customHeight="1">
       <c r="A62" s="11" t="s">
         <v>55</v>
       </c>
@@ -15852,7 +15846,7 @@
       <c r="V62" s="8"/>
       <c r="W62" s="2"/>
     </row>
-    <row r="63" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="63" spans="1:23" ht="48" customHeight="1">
       <c r="A63" s="11" t="s">
         <v>55</v>
       </c>
@@ -15917,7 +15911,7 @@
       <c r="V63" s="8"/>
       <c r="W63" s="2"/>
     </row>
-    <row r="64" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="64" spans="1:23" ht="48" customHeight="1">
       <c r="A64" s="11" t="s">
         <v>55</v>
       </c>
@@ -15982,7 +15976,7 @@
       <c r="V64" s="8"/>
       <c r="W64" s="2"/>
     </row>
-    <row r="65" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="65" spans="1:23" ht="75.95" customHeight="1">
       <c r="A65" s="11" t="s">
         <v>55</v>
       </c>
@@ -16047,7 +16041,7 @@
       <c r="V65" s="8"/>
       <c r="W65" s="2"/>
     </row>
-    <row r="66" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="66" spans="1:23" ht="75.95" customHeight="1">
       <c r="A66" s="11" t="s">
         <v>55</v>
       </c>
@@ -16112,7 +16106,7 @@
       <c r="V66" s="8"/>
       <c r="W66" s="2"/>
     </row>
-    <row r="67" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="67" spans="1:23" ht="48" customHeight="1">
       <c r="A67" s="11" t="s">
         <v>55</v>
       </c>
@@ -16177,7 +16171,7 @@
       <c r="V67" s="8"/>
       <c r="W67" s="2"/>
     </row>
-    <row r="68" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="68" spans="1:23" ht="48" customHeight="1">
       <c r="A68" s="11" t="s">
         <v>55</v>
       </c>
@@ -16242,7 +16236,7 @@
       <c r="V68" s="8"/>
       <c r="W68" s="2"/>
     </row>
-    <row r="69" spans="1:23" ht="104.1" hidden="1" customHeight="1">
+    <row r="69" spans="1:23" ht="104.1" customHeight="1">
       <c r="A69" s="11" t="s">
         <v>55</v>
       </c>
@@ -16307,7 +16301,7 @@
       <c r="V69" s="8"/>
       <c r="W69" s="2"/>
     </row>
-    <row r="70" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="70" spans="1:23" ht="48" customHeight="1">
       <c r="A70" s="11" t="s">
         <v>55</v>
       </c>
@@ -16372,7 +16366,7 @@
       <c r="V70" s="8"/>
       <c r="W70" s="2"/>
     </row>
-    <row r="71" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="71" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A71" s="11" t="s">
         <v>55</v>
       </c>
@@ -16437,7 +16431,7 @@
       <c r="V71" s="8"/>
       <c r="W71" s="2"/>
     </row>
-    <row r="72" spans="1:23" ht="104.1" hidden="1" customHeight="1">
+    <row r="72" spans="1:23" ht="104.1" customHeight="1">
       <c r="A72" s="11" t="s">
         <v>55</v>
       </c>
@@ -16502,7 +16496,7 @@
       <c r="V72" s="8"/>
       <c r="W72" s="2"/>
     </row>
-    <row r="73" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="73" spans="1:23" ht="48" customHeight="1">
       <c r="A73" s="11" t="s">
         <v>55</v>
       </c>
@@ -16567,7 +16561,7 @@
       <c r="V73" s="8"/>
       <c r="W73" s="2"/>
     </row>
-    <row r="74" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="74" spans="1:23" ht="48" customHeight="1">
       <c r="A74" s="11" t="s">
         <v>55</v>
       </c>
@@ -16632,7 +16626,7 @@
       <c r="V74" s="8"/>
       <c r="W74" s="2"/>
     </row>
-    <row r="75" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="75" spans="1:23" ht="48" customHeight="1">
       <c r="A75" s="11" t="s">
         <v>55</v>
       </c>
@@ -16697,7 +16691,7 @@
       <c r="V75" s="8"/>
       <c r="W75" s="2"/>
     </row>
-    <row r="76" spans="1:23" ht="104.1" hidden="1" customHeight="1">
+    <row r="76" spans="1:23" ht="104.1" customHeight="1">
       <c r="A76" s="11" t="s">
         <v>55</v>
       </c>
@@ -16762,7 +16756,7 @@
       <c r="V76" s="8"/>
       <c r="W76" s="2"/>
     </row>
-    <row r="77" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="77" spans="1:23" ht="48" customHeight="1">
       <c r="A77" s="11" t="s">
         <v>55</v>
       </c>
@@ -16827,7 +16821,7 @@
       <c r="V77" s="8"/>
       <c r="W77" s="2"/>
     </row>
-    <row r="78" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="78" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A78" s="11" t="s">
         <v>55</v>
       </c>
@@ -16892,7 +16886,7 @@
       <c r="V78" s="8"/>
       <c r="W78" s="2"/>
     </row>
-    <row r="79" spans="1:23" ht="104.1" hidden="1" customHeight="1">
+    <row r="79" spans="1:23" ht="104.1" customHeight="1">
       <c r="A79" s="11" t="s">
         <v>55</v>
       </c>
@@ -16957,7 +16951,7 @@
       <c r="V79" s="8"/>
       <c r="W79" s="2"/>
     </row>
-    <row r="80" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="80" spans="1:23" ht="48" customHeight="1">
       <c r="A80" s="11" t="s">
         <v>55</v>
       </c>
@@ -17022,7 +17016,7 @@
       <c r="V80" s="8"/>
       <c r="W80" s="2"/>
     </row>
-    <row r="81" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="81" spans="1:23" ht="48" customHeight="1">
       <c r="A81" s="11" t="s">
         <v>55</v>
       </c>
@@ -17087,7 +17081,7 @@
       <c r="V81" s="8"/>
       <c r="W81" s="2"/>
     </row>
-    <row r="82" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="82" spans="1:23" ht="48" customHeight="1">
       <c r="A82" s="11" t="s">
         <v>55</v>
       </c>
@@ -17152,7 +17146,7 @@
       <c r="V82" s="8"/>
       <c r="W82" s="2"/>
     </row>
-    <row r="83" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="83" spans="1:23" ht="48" customHeight="1">
       <c r="A83" s="11" t="s">
         <v>55</v>
       </c>
@@ -17217,7 +17211,7 @@
       <c r="V83" s="8"/>
       <c r="W83" s="2"/>
     </row>
-    <row r="84" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="84" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A84" s="11" t="s">
         <v>55</v>
       </c>
@@ -17282,7 +17276,7 @@
       <c r="V84" s="8"/>
       <c r="W84" s="2"/>
     </row>
-    <row r="85" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="85" spans="1:23" ht="48" customHeight="1">
       <c r="A85" s="11" t="s">
         <v>55</v>
       </c>
@@ -17347,7 +17341,7 @@
       <c r="V85" s="8"/>
       <c r="W85" s="2"/>
     </row>
-    <row r="86" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="86" spans="1:23" ht="48" customHeight="1">
       <c r="A86" s="11" t="s">
         <v>55</v>
       </c>
@@ -17412,7 +17406,7 @@
       <c r="V86" s="8"/>
       <c r="W86" s="2"/>
     </row>
-    <row r="87" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="87" spans="1:23" ht="48" customHeight="1">
       <c r="A87" s="11" t="s">
         <v>55</v>
       </c>
@@ -17477,7 +17471,7 @@
       <c r="V87" s="8"/>
       <c r="W87" s="2"/>
     </row>
-    <row r="88" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="88" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A88" s="11" t="s">
         <v>55</v>
       </c>
@@ -17542,7 +17536,7 @@
       <c r="V88" s="8"/>
       <c r="W88" s="2"/>
     </row>
-    <row r="89" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="89" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A89" s="11" t="s">
         <v>55</v>
       </c>
@@ -17607,7 +17601,7 @@
       <c r="V89" s="8"/>
       <c r="W89" s="2"/>
     </row>
-    <row r="90" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="90" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A90" s="11" t="s">
         <v>55</v>
       </c>
@@ -17672,7 +17666,7 @@
       <c r="V90" s="8"/>
       <c r="W90" s="2"/>
     </row>
-    <row r="91" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="91" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A91" s="11" t="s">
         <v>55</v>
       </c>
@@ -17737,7 +17731,7 @@
       <c r="V91" s="8"/>
       <c r="W91" s="2"/>
     </row>
-    <row r="92" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="92" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A92" s="11" t="s">
         <v>55</v>
       </c>
@@ -17802,7 +17796,7 @@
       <c r="V92" s="8"/>
       <c r="W92" s="2"/>
     </row>
-    <row r="93" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="93" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A93" s="11" t="s">
         <v>55</v>
       </c>
@@ -17867,7 +17861,7 @@
       <c r="V93" s="8"/>
       <c r="W93" s="2"/>
     </row>
-    <row r="94" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="94" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A94" s="11" t="s">
         <v>55</v>
       </c>
@@ -17932,7 +17926,7 @@
       <c r="V94" s="8"/>
       <c r="W94" s="2"/>
     </row>
-    <row r="95" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="95" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A95" s="11" t="s">
         <v>55</v>
       </c>
@@ -17997,7 +17991,7 @@
       <c r="V95" s="8"/>
       <c r="W95" s="2"/>
     </row>
-    <row r="96" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="96" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A96" s="11" t="s">
         <v>55</v>
       </c>
@@ -18062,7 +18056,7 @@
       <c r="V96" s="8"/>
       <c r="W96" s="2"/>
     </row>
-    <row r="97" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="97" spans="1:23" ht="48" customHeight="1">
       <c r="A97" s="11" t="s">
         <v>55</v>
       </c>
@@ -18127,7 +18121,7 @@
       <c r="V97" s="8"/>
       <c r="W97" s="2"/>
     </row>
-    <row r="98" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="98" spans="1:23" ht="48" customHeight="1">
       <c r="A98" s="11" t="s">
         <v>55</v>
       </c>
@@ -18192,7 +18186,7 @@
       <c r="V98" s="8"/>
       <c r="W98" s="2"/>
     </row>
-    <row r="99" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="99" spans="1:23" ht="48" customHeight="1">
       <c r="A99" s="11" t="s">
         <v>55</v>
       </c>
@@ -18257,7 +18251,7 @@
       <c r="V99" s="8"/>
       <c r="W99" s="2"/>
     </row>
-    <row r="100" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="100" spans="1:23" ht="62.1" customHeight="1">
       <c r="A100" s="11" t="s">
         <v>55</v>
       </c>
@@ -18324,7 +18318,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="101" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="101" spans="1:23" ht="62.1" customHeight="1">
       <c r="A101" s="11" t="s">
         <v>55</v>
       </c>
@@ -18391,7 +18385,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="102" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="102" spans="1:23" ht="62.1" customHeight="1">
       <c r="A102" s="11" t="s">
         <v>55</v>
       </c>
@@ -18456,7 +18450,7 @@
       <c r="V102" s="8"/>
       <c r="W102" s="2"/>
     </row>
-    <row r="103" spans="1:23" ht="113.25" hidden="1">
+    <row r="103" spans="1:23" ht="113.25">
       <c r="A103" s="11" t="s">
         <v>55</v>
       </c>
@@ -18521,7 +18515,7 @@
       <c r="V103" s="8"/>
       <c r="W103" s="2"/>
     </row>
-    <row r="104" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="104" spans="1:23" ht="62.1" customHeight="1">
       <c r="A104" s="11" t="s">
         <v>55</v>
       </c>
@@ -18588,7 +18582,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="105" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="105" spans="1:23" ht="62.1" customHeight="1">
       <c r="A105" s="11" t="s">
         <v>55</v>
       </c>
@@ -18655,7 +18649,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="106" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="106" spans="1:23" ht="62.1" customHeight="1">
       <c r="A106" s="11" t="s">
         <v>55</v>
       </c>
@@ -18722,7 +18716,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="107" spans="1:23" ht="62.1" customHeight="1">
       <c r="A107" s="11" t="s">
         <v>55</v>
       </c>
@@ -18789,7 +18783,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="108" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="108" spans="1:23" ht="90" customHeight="1">
       <c r="A108" s="11" t="s">
         <v>55</v>
       </c>
@@ -18854,7 +18848,7 @@
       <c r="V108" s="8"/>
       <c r="W108" s="2"/>
     </row>
-    <row r="109" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="109" spans="1:23" ht="62.1" customHeight="1">
       <c r="A109" s="11" t="s">
         <v>55</v>
       </c>
@@ -18921,7 +18915,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="110" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="110" spans="1:23" ht="62.1" customHeight="1">
       <c r="A110" s="11" t="s">
         <v>55</v>
       </c>
@@ -18988,7 +18982,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="111" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="111" spans="1:23" ht="75.95" customHeight="1">
       <c r="A111" s="11" t="s">
         <v>55</v>
       </c>
@@ -19053,7 +19047,7 @@
       <c r="V111" s="8"/>
       <c r="W111" s="2"/>
     </row>
-    <row r="112" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="112" spans="1:23" ht="62.1" customHeight="1">
       <c r="A112" s="11" t="s">
         <v>55</v>
       </c>
@@ -19118,7 +19112,7 @@
       <c r="V112" s="8"/>
       <c r="W112" s="2"/>
     </row>
-    <row r="113" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="113" spans="1:23" ht="62.1" customHeight="1">
       <c r="A113" s="11" t="s">
         <v>55</v>
       </c>
@@ -19183,7 +19177,7 @@
       <c r="V113" s="8"/>
       <c r="W113" s="2"/>
     </row>
-    <row r="114" spans="1:23" ht="104.1" hidden="1" customHeight="1">
+    <row r="114" spans="1:23" ht="104.1" customHeight="1">
       <c r="A114" s="11" t="s">
         <v>55</v>
       </c>
@@ -19248,7 +19242,7 @@
       <c r="V114" s="8"/>
       <c r="W114" s="2"/>
     </row>
-    <row r="115" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="115" spans="1:23" ht="62.1" customHeight="1">
       <c r="A115" s="11" t="s">
         <v>55</v>
       </c>
@@ -19313,7 +19307,7 @@
       <c r="V115" s="8"/>
       <c r="W115" s="2"/>
     </row>
-    <row r="116" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="116" spans="1:23" ht="62.1" customHeight="1">
       <c r="A116" s="11" t="s">
         <v>55</v>
       </c>
@@ -19378,7 +19372,7 @@
       <c r="V116" s="8"/>
       <c r="W116" s="2"/>
     </row>
-    <row r="117" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="117" spans="1:23" ht="62.1" customHeight="1">
       <c r="A117" s="11" t="s">
         <v>55</v>
       </c>
@@ -19445,7 +19439,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="118" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="118" spans="1:23" ht="62.1" customHeight="1">
       <c r="A118" s="11" t="s">
         <v>55</v>
       </c>
@@ -19512,7 +19506,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="119" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="119" spans="1:23" ht="90" customHeight="1">
       <c r="A119" s="11" t="s">
         <v>55</v>
       </c>
@@ -19577,7 +19571,7 @@
       <c r="V119" s="8"/>
       <c r="W119" s="2"/>
     </row>
-    <row r="120" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="120" spans="1:23" ht="48" customHeight="1">
       <c r="A120" s="11" t="s">
         <v>55</v>
       </c>
@@ -19644,7 +19638,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="121" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="121" spans="1:23" ht="48" customHeight="1">
       <c r="A121" s="11" t="s">
         <v>55</v>
       </c>
@@ -19709,7 +19703,7 @@
       <c r="V121" s="8"/>
       <c r="W121" s="2"/>
     </row>
-    <row r="122" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="122" spans="1:23" ht="48" customHeight="1">
       <c r="A122" s="11" t="s">
         <v>55</v>
       </c>
@@ -19776,7 +19770,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="123" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="123" spans="1:23" ht="48" customHeight="1">
       <c r="A123" s="11" t="s">
         <v>55</v>
       </c>
@@ -19843,7 +19837,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="124" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="124" spans="1:23" ht="48" customHeight="1">
       <c r="A124" s="11" t="s">
         <v>55</v>
       </c>
@@ -19910,7 +19904,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="125" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="125" spans="1:23" ht="48" customHeight="1">
       <c r="A125" s="11" t="s">
         <v>55</v>
       </c>
@@ -19975,7 +19969,7 @@
       <c r="V125" s="8"/>
       <c r="W125" s="2"/>
     </row>
-    <row r="126" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="126" spans="1:23" ht="48" customHeight="1">
       <c r="A126" s="11" t="s">
         <v>55</v>
       </c>
@@ -20040,7 +20034,7 @@
       <c r="V126" s="8"/>
       <c r="W126" s="2"/>
     </row>
-    <row r="127" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="127" spans="1:23" ht="48" customHeight="1">
       <c r="A127" s="11" t="s">
         <v>55</v>
       </c>
@@ -20105,7 +20099,7 @@
       <c r="V127" s="8"/>
       <c r="W127" s="2"/>
     </row>
-    <row r="128" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="128" spans="1:23" ht="48" customHeight="1">
       <c r="A128" s="11" t="s">
         <v>55</v>
       </c>
@@ -20170,7 +20164,7 @@
       <c r="V128" s="8"/>
       <c r="W128" s="2"/>
     </row>
-    <row r="129" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="129" spans="1:23" ht="48" customHeight="1">
       <c r="A129" s="11" t="s">
         <v>55</v>
       </c>
@@ -20235,7 +20229,7 @@
       <c r="V129" s="8"/>
       <c r="W129" s="2"/>
     </row>
-    <row r="130" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="130" spans="1:23" ht="75.95" customHeight="1">
       <c r="A130" s="11" t="s">
         <v>55</v>
       </c>
@@ -20300,7 +20294,7 @@
       <c r="V130" s="8"/>
       <c r="W130" s="2"/>
     </row>
-    <row r="131" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="131" spans="1:23" ht="48" customHeight="1">
       <c r="A131" s="11" t="s">
         <v>55</v>
       </c>
@@ -20367,7 +20361,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="132" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="132" spans="1:23" ht="48" customHeight="1">
       <c r="A132" s="11" t="s">
         <v>55</v>
       </c>
@@ -20434,7 +20428,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="133" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="133" spans="1:23" ht="62.1" customHeight="1">
       <c r="A133" s="11" t="s">
         <v>55</v>
       </c>
@@ -20499,7 +20493,7 @@
       <c r="V133" s="8"/>
       <c r="W133" s="2"/>
     </row>
-    <row r="134" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="134" spans="1:23" ht="62.1" customHeight="1">
       <c r="A134" s="11" t="s">
         <v>55</v>
       </c>
@@ -20564,7 +20558,7 @@
       <c r="V134" s="8"/>
       <c r="W134" s="2"/>
     </row>
-    <row r="135" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="135" spans="1:23" ht="62.1" customHeight="1">
       <c r="A135" s="11" t="s">
         <v>55</v>
       </c>
@@ -20629,7 +20623,7 @@
       <c r="V135" s="8"/>
       <c r="W135" s="2"/>
     </row>
-    <row r="136" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="136" spans="1:23" ht="48" customHeight="1">
       <c r="A136" s="11" t="s">
         <v>55</v>
       </c>
@@ -20694,7 +20688,7 @@
       <c r="V136" s="8"/>
       <c r="W136" s="2"/>
     </row>
-    <row r="137" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="137" spans="1:23" ht="48" customHeight="1">
       <c r="A137" s="11" t="s">
         <v>55</v>
       </c>
@@ -20759,7 +20753,7 @@
       <c r="V137" s="8"/>
       <c r="W137" s="2"/>
     </row>
-    <row r="138" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="138" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A138" s="11" t="s">
         <v>55</v>
       </c>
@@ -20824,7 +20818,7 @@
       <c r="V138" s="8"/>
       <c r="W138" s="2"/>
     </row>
-    <row r="139" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="139" spans="1:23" ht="48" customHeight="1">
       <c r="A139" s="11" t="s">
         <v>55</v>
       </c>
@@ -20889,7 +20883,7 @@
       <c r="V139" s="8"/>
       <c r="W139" s="2"/>
     </row>
-    <row r="140" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="140" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A140" s="11" t="s">
         <v>55</v>
       </c>
@@ -20954,7 +20948,7 @@
       <c r="V140" s="8"/>
       <c r="W140" s="2"/>
     </row>
-    <row r="141" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="141" spans="1:23" ht="48" customHeight="1">
       <c r="A141" s="11" t="s">
         <v>55</v>
       </c>
@@ -21019,7 +21013,7 @@
       <c r="V141" s="8"/>
       <c r="W141" s="2"/>
     </row>
-    <row r="142" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="142" spans="1:23" ht="48" customHeight="1">
       <c r="A142" s="11" t="s">
         <v>55</v>
       </c>
@@ -21084,7 +21078,7 @@
       <c r="V142" s="8"/>
       <c r="W142" s="2"/>
     </row>
-    <row r="143" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="143" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A143" s="11" t="s">
         <v>55</v>
       </c>
@@ -21149,7 +21143,7 @@
       <c r="V143" s="8"/>
       <c r="W143" s="2"/>
     </row>
-    <row r="144" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="144" spans="1:23" ht="48" customHeight="1">
       <c r="A144" s="11" t="s">
         <v>55</v>
       </c>
@@ -21214,7 +21208,7 @@
       <c r="V144" s="8"/>
       <c r="W144" s="2"/>
     </row>
-    <row r="145" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="145" spans="1:23" ht="48" customHeight="1">
       <c r="A145" s="11" t="s">
         <v>55</v>
       </c>
@@ -21279,7 +21273,7 @@
       <c r="V145" s="8"/>
       <c r="W145" s="2"/>
     </row>
-    <row r="146" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="146" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A146" s="11" t="s">
         <v>55</v>
       </c>
@@ -21344,7 +21338,7 @@
       <c r="V146" s="8"/>
       <c r="W146" s="2"/>
     </row>
-    <row r="147" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="147" spans="1:23" ht="48" customHeight="1">
       <c r="A147" s="11" t="s">
         <v>55</v>
       </c>
@@ -21409,7 +21403,7 @@
       <c r="V147" s="8"/>
       <c r="W147" s="2"/>
     </row>
-    <row r="148" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="148" spans="1:23" ht="48" customHeight="1">
       <c r="A148" s="11" t="s">
         <v>55</v>
       </c>
@@ -21474,7 +21468,7 @@
       <c r="V148" s="8"/>
       <c r="W148" s="2"/>
     </row>
-    <row r="149" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="149" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A149" s="11" t="s">
         <v>55</v>
       </c>
@@ -21539,7 +21533,7 @@
       <c r="V149" s="8"/>
       <c r="W149" s="2"/>
     </row>
-    <row r="150" spans="1:23" ht="75.95" hidden="1" customHeight="1">
+    <row r="150" spans="1:23" ht="75.95" customHeight="1">
       <c r="A150" s="11" t="s">
         <v>55</v>
       </c>
@@ -21606,7 +21600,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="151" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A151" s="11" t="s">
         <v>55</v>
       </c>
@@ -21671,7 +21665,7 @@
       <c r="V151" s="8"/>
       <c r="W151" s="2"/>
     </row>
-    <row r="152" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="152" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A152" s="11" t="s">
         <v>55</v>
       </c>
@@ -21736,7 +21730,7 @@
       <c r="V152" s="8"/>
       <c r="W152" s="2"/>
     </row>
-    <row r="153" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="153" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A153" s="11" t="s">
         <v>55</v>
       </c>
@@ -21801,7 +21795,7 @@
       <c r="V153" s="8"/>
       <c r="W153" s="2"/>
     </row>
-    <row r="154" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="154" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A154" s="11" t="s">
         <v>55</v>
       </c>
@@ -21866,7 +21860,7 @@
       <c r="V154" s="8"/>
       <c r="W154" s="2"/>
     </row>
-    <row r="155" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="155" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A155" s="11" t="s">
         <v>55</v>
       </c>
@@ -21931,7 +21925,7 @@
       <c r="V155" s="8"/>
       <c r="W155" s="2"/>
     </row>
-    <row r="156" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="156" spans="1:23" ht="48" customHeight="1">
       <c r="A156" s="11" t="s">
         <v>55</v>
       </c>
@@ -21996,7 +21990,7 @@
       <c r="V156" s="8"/>
       <c r="W156" s="2"/>
     </row>
-    <row r="157" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="157" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A157" s="11" t="s">
         <v>55</v>
       </c>
@@ -22061,7 +22055,7 @@
       <c r="V157" s="8"/>
       <c r="W157" s="2"/>
     </row>
-    <row r="158" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="158" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A158" s="11" t="s">
         <v>55</v>
       </c>
@@ -22126,7 +22120,7 @@
       <c r="V158" s="8"/>
       <c r="W158" s="2"/>
     </row>
-    <row r="159" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="159" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A159" s="11" t="s">
         <v>55</v>
       </c>
@@ -22191,7 +22185,7 @@
       <c r="V159" s="8"/>
       <c r="W159" s="2"/>
     </row>
-    <row r="160" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="160" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A160" s="11" t="s">
         <v>55</v>
       </c>
@@ -22256,7 +22250,7 @@
       <c r="V160" s="8"/>
       <c r="W160" s="2"/>
     </row>
-    <row r="161" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="161" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A161" s="11" t="s">
         <v>55</v>
       </c>
@@ -22321,7 +22315,7 @@
       <c r="V161" s="8"/>
       <c r="W161" s="2"/>
     </row>
-    <row r="162" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="162" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A162" s="11" t="s">
         <v>55</v>
       </c>
@@ -22386,7 +22380,7 @@
       <c r="V162" s="8"/>
       <c r="W162" s="2"/>
     </row>
-    <row r="163" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="163" spans="1:23" ht="48" customHeight="1">
       <c r="A163" s="11" t="s">
         <v>55</v>
       </c>
@@ -22451,7 +22445,7 @@
       <c r="V163" s="8"/>
       <c r="W163" s="2"/>
     </row>
-    <row r="164" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="164" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A164" s="11" t="s">
         <v>55</v>
       </c>
@@ -22516,7 +22510,7 @@
       <c r="V164" s="8"/>
       <c r="W164" s="2"/>
     </row>
-    <row r="165" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="165" spans="1:23" ht="48" customHeight="1">
       <c r="A165" s="11" t="s">
         <v>55</v>
       </c>
@@ -22581,7 +22575,7 @@
       <c r="V165" s="8"/>
       <c r="W165" s="2"/>
     </row>
-    <row r="166" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="166" spans="1:23" ht="90" customHeight="1">
       <c r="A166" s="11" t="s">
         <v>55</v>
       </c>
@@ -22646,7 +22640,7 @@
       <c r="V166" s="8"/>
       <c r="W166" s="2"/>
     </row>
-    <row r="167" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="167" spans="1:23" ht="62.1" customHeight="1">
       <c r="A167" s="11" t="s">
         <v>55</v>
       </c>
@@ -22711,7 +22705,7 @@
       <c r="V167" s="8"/>
       <c r="W167" s="2"/>
     </row>
-    <row r="168" spans="1:23" ht="62.1" hidden="1" customHeight="1">
+    <row r="168" spans="1:23" ht="62.1" customHeight="1">
       <c r="A168" s="11" t="s">
         <v>55</v>
       </c>
@@ -22776,7 +22770,7 @@
       <c r="V168" s="8"/>
       <c r="W168" s="2"/>
     </row>
-    <row r="169" spans="1:23" ht="90" hidden="1" customHeight="1">
+    <row r="169" spans="1:23" ht="90" customHeight="1">
       <c r="A169" s="11" t="s">
         <v>55</v>
       </c>
@@ -23239,7 +23233,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="176" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="176" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A176" s="11" t="s">
         <v>55</v>
       </c>
@@ -23306,7 +23300,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="177" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="177" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A177" s="11" t="s">
         <v>55</v>
       </c>
@@ -23371,7 +23365,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="178" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="178" spans="1:23" ht="48" customHeight="1">
       <c r="A178" s="11" t="s">
         <v>55</v>
       </c>
@@ -23438,7 +23432,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="179" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="179" spans="1:23" ht="48" customHeight="1">
       <c r="A179" s="11" t="s">
         <v>55</v>
       </c>
@@ -23505,7 +23499,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="180" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="180" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A180" s="11" t="s">
         <v>55</v>
       </c>
@@ -23572,7 +23566,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="181" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="181" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A181" s="11" t="s">
         <v>55</v>
       </c>
@@ -23639,7 +23633,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="182" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="182" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A182" s="11" t="s">
         <v>55</v>
       </c>
@@ -23706,7 +23700,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="183" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="183" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A183" s="11" t="s">
         <v>55</v>
       </c>
@@ -23773,7 +23767,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="184" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="184" spans="1:23" ht="48" customHeight="1">
       <c r="A184" s="11" t="s">
         <v>55</v>
       </c>
@@ -23840,7 +23834,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="185" spans="1:23" ht="48" hidden="1" customHeight="1">
+    <row r="185" spans="1:23" ht="48" customHeight="1">
       <c r="A185" s="11" t="s">
         <v>55</v>
       </c>
@@ -23907,7 +23901,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="186" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="186" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A186" s="11" t="s">
         <v>55</v>
       </c>
@@ -23974,7 +23968,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="33.950000000000003" hidden="1" customHeight="1">
+    <row r="187" spans="1:23" ht="33.950000000000003" customHeight="1">
       <c r="A187" s="11" t="s">
         <v>55</v>
       </c>
@@ -24041,7 +24035,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="188" spans="1:23" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="188" spans="1:23" ht="36.950000000000003" customHeight="1">
       <c r="A188" s="11" t="s">
         <v>55</v>
       </c>
@@ -24105,7 +24099,7 @@
       <c r="U188" s="22"/>
       <c r="V188" s="22"/>
     </row>
-    <row r="189" spans="1:23" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="189" spans="1:23" ht="36.950000000000003" customHeight="1">
       <c r="A189" s="11" t="s">
         <v>55</v>
       </c>
@@ -24169,7 +24163,7 @@
       <c r="U189" s="22"/>
       <c r="V189" s="22"/>
     </row>
-    <row r="190" spans="1:23" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="190" spans="1:23" ht="36.950000000000003" customHeight="1">
       <c r="A190" s="11" t="s">
         <v>55</v>
       </c>
@@ -24233,7 +24227,7 @@
       <c r="U190" s="22"/>
       <c r="V190" s="22"/>
     </row>
-    <row r="191" spans="1:23" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="191" spans="1:23" ht="36.950000000000003" customHeight="1">
       <c r="A191" s="11" t="s">
         <v>55</v>
       </c>
@@ -24297,7 +24291,7 @@
       <c r="U191" s="22"/>
       <c r="V191" s="22"/>
     </row>
-    <row r="192" spans="1:23" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="192" spans="1:23" ht="36.950000000000003" customHeight="1">
       <c r="A192" s="11" t="s">
         <v>55</v>
       </c>
@@ -24361,7 +24355,7 @@
       <c r="U192" s="22"/>
       <c r="V192" s="22"/>
     </row>
-    <row r="193" spans="1:22" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="193" spans="1:22" ht="36.950000000000003" customHeight="1">
       <c r="A193" s="19" t="s">
         <v>55</v>
       </c>
@@ -24425,7 +24419,7 @@
       <c r="U193" s="22"/>
       <c r="V193" s="22"/>
     </row>
-    <row r="194" spans="1:22" ht="36.950000000000003" hidden="1" customHeight="1">
+    <row r="194" spans="1:22" ht="36.950000000000003" customHeight="1">
       <c r="A194" s="19" t="s">
         <v>55</v>
       </c>
@@ -56644,6 +56638,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008EE62A8A34B8614BBAFE91C998988572" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="993acd0ebe3d4b41eb805c6c9afb9eef">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b045652c-0488-4d93-85f8-6539f1c4bf92" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aaa2b9e46cddab28a3fa9210c8df6f8" ns2:_="">
     <xsd:import namespace="b045652c-0488-4d93-85f8-6539f1c4bf92"/>
@@ -56821,25 +56824,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8AECCB7-3CAC-4316-BF6D-E3D6AA1CC50A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78DE77EE-20FA-40B5-A872-075A71CDA5B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A5F59B6-7897-4C01-9AAC-C49229741DBB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A5F59B6-7897-4C01-9AAC-C49229741DBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78DE77EE-20FA-40B5-A872-075A71CDA5B2}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
